--- a/public/downloads/SniderRevealing2018.xlsx
+++ b/public/downloads/SniderRevealing2018.xlsx
@@ -8,29 +8,31 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="ORB-v3" sheetId="12" r:id="rId12"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="13" r:id="rId13"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="16" r:id="rId16"/>
-    <sheet name="UMA-s-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="ORB-v3" sheetId="14" r:id="rId14"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="15" r:id="rId15"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="18" r:id="rId18"/>
+    <sheet name="UMA-s-1p1_omat" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="56">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -62,10 +64,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -167,16 +169,37 @@
     <t>Adsorbate_name</t>
   </si>
   <si>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
+  </si>
+  <si>
     <t>CO</t>
   </si>
   <si>
     <t>HO</t>
   </si>
   <si>
-    <t>CH3O</t>
+    <t>CH2</t>
   </si>
   <si>
-    <t>CH2</t>
+    <t>CH3O</t>
   </si>
 </sst>
 </file>
@@ -662,10 +685,10 @@
         <v>44</v>
       </c>
       <c r="N3" s="5">
-        <v>222.0496356487274</v>
+        <v>222049.6356487274</v>
       </c>
       <c r="O3" s="4">
-        <v>0.03343617461959455</v>
+        <v>33.43617461959455</v>
       </c>
       <c r="P3" s="5">
         <v>6641</v>
@@ -712,10 +735,10 @@
         <v>44</v>
       </c>
       <c r="N4" s="5">
-        <v>283.673629283905</v>
+        <v>283673.629283905</v>
       </c>
       <c r="O4" s="4">
-        <v>0.04879986741508774</v>
+        <v>48.79986741508774</v>
       </c>
       <c r="P4" s="5">
         <v>5813</v>
@@ -762,10 +785,10 @@
         <v>44</v>
       </c>
       <c r="N5" s="5">
-        <v>745.6472742557526</v>
+        <v>745647.2742557526</v>
       </c>
       <c r="O5" s="4">
-        <v>0.1539321375424758</v>
+        <v>153.9321375424757</v>
       </c>
       <c r="P5" s="5">
         <v>4844</v>
@@ -812,10 +835,10 @@
         <v>44</v>
       </c>
       <c r="N6" s="5">
-        <v>563.0174014568329</v>
+        <v>563017.4014568329</v>
       </c>
       <c r="O6" s="4">
-        <v>0.08433454185992105</v>
+        <v>84.33454185992105</v>
       </c>
       <c r="P6" s="5">
         <v>6676</v>
@@ -862,10 +885,10 @@
         <v>44</v>
       </c>
       <c r="N7" s="5">
-        <v>668.4745712280273</v>
+        <v>668474.5712280273</v>
       </c>
       <c r="O7" s="4">
-        <v>0.1631619651520692</v>
+        <v>163.1619651520691</v>
       </c>
       <c r="P7" s="5">
         <v>4097</v>
@@ -912,10 +935,10 @@
         <v>44</v>
       </c>
       <c r="N8" s="5">
-        <v>58.95068311691284</v>
+        <v>58950.68311691284</v>
       </c>
       <c r="O8" s="4">
-        <v>0.01273507952406845</v>
+        <v>12.73507952406845</v>
       </c>
       <c r="P8" s="5">
         <v>4629</v>
@@ -962,10 +985,10 @@
         <v>44</v>
       </c>
       <c r="N9" s="5">
-        <v>195.6977372169495</v>
+        <v>195697.7372169495</v>
       </c>
       <c r="O9" s="4">
-        <v>0.0328131685474429</v>
+        <v>32.8131685474429</v>
       </c>
       <c r="P9" s="5">
         <v>5964</v>
@@ -1012,10 +1035,10 @@
         <v>44</v>
       </c>
       <c r="N10" s="5">
-        <v>349.4786887168884</v>
+        <v>349478.6887168884</v>
       </c>
       <c r="O10" s="4">
-        <v>0.08459905318733682</v>
+        <v>84.59905318733682</v>
       </c>
       <c r="P10" s="5">
         <v>4131</v>
@@ -1062,10 +1085,10 @@
         <v>44</v>
       </c>
       <c r="N11" s="5">
-        <v>251.8267476558685</v>
+        <v>251826.7476558685</v>
       </c>
       <c r="O11" s="4">
-        <v>0.04264635862080754</v>
+        <v>42.64635862080754</v>
       </c>
       <c r="P11" s="5">
         <v>5905</v>
@@ -1112,10 +1135,10 @@
         <v>44</v>
       </c>
       <c r="N12" s="5">
-        <v>181.0766146183014</v>
+        <v>181076.6146183014</v>
       </c>
       <c r="O12" s="4">
-        <v>0.01898674788909525</v>
+        <v>18.98674788909525</v>
       </c>
       <c r="P12" s="5">
         <v>9537</v>
@@ -1162,10 +1185,10 @@
         <v>44</v>
       </c>
       <c r="N13" s="5">
-        <v>503.2435042858124</v>
+        <v>503243.5042858124</v>
       </c>
       <c r="O13" s="4">
-        <v>0.07720827006532868</v>
+        <v>77.20827006532868</v>
       </c>
       <c r="P13" s="5">
         <v>6518</v>
@@ -1212,10 +1235,10 @@
         <v>44</v>
       </c>
       <c r="N14" s="5">
-        <v>212.7635855674744</v>
+        <v>212763.5855674744</v>
       </c>
       <c r="O14" s="4">
-        <v>0.2287780489972843</v>
+        <v>228.7780489972843</v>
       </c>
       <c r="P14" s="5">
         <v>930</v>
@@ -1262,10 +1285,10 @@
         <v>44</v>
       </c>
       <c r="N15" s="5">
-        <v>1208.461856365204</v>
+        <v>1208461.856365204</v>
       </c>
       <c r="O15" s="4">
-        <v>0.2298767084582849</v>
+        <v>229.8767084582849</v>
       </c>
       <c r="P15" s="5">
         <v>5257</v>
@@ -1312,10 +1335,10 @@
         <v>44</v>
       </c>
       <c r="N16" s="5">
-        <v>120.2163820266724</v>
+        <v>120216.3820266724</v>
       </c>
       <c r="O16" s="4">
-        <v>0.09894352430178795</v>
+        <v>98.94352430178795</v>
       </c>
       <c r="P16" s="5">
         <v>1215</v>
@@ -1362,10 +1385,10 @@
         <v>44</v>
       </c>
       <c r="N17" s="5">
-        <v>502.6158752441406</v>
+        <v>502615.8752441406</v>
       </c>
       <c r="O17" s="4">
-        <v>0.09828233774816986</v>
+        <v>98.28233774816985</v>
       </c>
       <c r="P17" s="5">
         <v>5114</v>
@@ -1393,7 +1416,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1404,9 +1427,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1440,8 +1469,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1463,25 +1500,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.193355597834185</v>
+        <v>0.298669344523239</v>
       </c>
       <c r="C3" s="4">
-        <v>0.193355597834185</v>
+        <v>0.298669344523239</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1941080367245838</v>
+        <v>0.288882139021684</v>
       </c>
       <c r="E3" s="4">
-        <v>84.67346938775511</v>
+        <v>81.48979591836735</v>
       </c>
       <c r="F3" s="4">
-        <v>89.75838926174497</v>
+        <v>87.42281879194631</v>
       </c>
       <c r="G3" s="5">
         <v>20</v>
@@ -1504,132 +1559,200 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.2191137208338517</v>
+      </c>
+      <c r="O3" s="5">
+        <v>20</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2117906267152352</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2117906267152352</v>
+      </c>
+      <c r="R3" s="5">
+        <v>20</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.07224944422220374</v>
+        <v>0.1555177566159034</v>
       </c>
       <c r="C4" s="4">
-        <v>0.07224944422220374</v>
+        <v>0.1558190126294164</v>
       </c>
       <c r="D4" s="4">
-        <v>0.05888918505003633</v>
+        <v>0.1584512813345568</v>
       </c>
       <c r="E4" s="4">
-        <v>84.13265306122449</v>
+        <v>78.85714285714286</v>
       </c>
       <c r="F4" s="4">
-        <v>88.70469798657719</v>
+        <v>82.53355704697987</v>
       </c>
       <c r="G4" s="5">
         <v>20</v>
       </c>
       <c r="H4" s="5">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.06219259478024202</v>
+      </c>
+      <c r="O4" s="5">
+        <v>18</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1528064524965191</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1528064524967672</v>
+      </c>
+      <c r="R4" s="5">
+        <v>18</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.1254253699879833</v>
+        <v>0.6446740862379556</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1254253699879833</v>
+        <v>0.696229585707357</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1126335797728153</v>
+        <v>0.6042380183290632</v>
       </c>
       <c r="E5" s="4">
-        <v>87.09183673469387</v>
+        <v>82.34693877551021</v>
       </c>
       <c r="F5" s="4">
-        <v>90.06711409395973</v>
+        <v>82.56711409395973</v>
       </c>
       <c r="G5" s="5">
         <v>2</v>
       </c>
       <c r="H5" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.6446740862379556</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.696229585707357</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.1338592622536368</v>
+        <v>0.6005282069775575</v>
       </c>
       <c r="C6" s="4">
-        <v>0.1914494735863315</v>
+        <v>0.6005282069775575</v>
       </c>
       <c r="D6" s="4">
-        <v>0.1001460070696325</v>
+        <v>0.5703303222093155</v>
       </c>
       <c r="E6" s="4">
-        <v>83.58843537414965</v>
+        <v>81.68367346938776</v>
       </c>
       <c r="F6" s="4">
-        <v>84.29530201342281</v>
+        <v>86.94630872483222</v>
       </c>
       <c r="G6" s="5">
         <v>2</v>
       </c>
       <c r="H6" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" s="5">
         <v>0</v>
       </c>
       <c r="J6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" s="5">
         <v>0</v>
       </c>
       <c r="L6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>2</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.6005282069775575</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.6005282069775575</v>
+      </c>
+      <c r="R6" s="5">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1640,6 +1763,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1647,7 +1771,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1658,9 +1782,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1694,8 +1824,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1717,34 +1855,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2710426463425392</v>
+        <v>0.6863954031010507</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2718191087832175</v>
+        <v>0.6904562368411765</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2943340030811669</v>
+        <v>0.7830121159626288</v>
       </c>
       <c r="E3" s="4">
-        <v>78.08503401360545</v>
+        <v>78.01020408163265</v>
       </c>
       <c r="F3" s="4">
-        <v>76.77069351230423</v>
+        <v>78.36744966442951</v>
       </c>
       <c r="G3" s="5">
         <v>20</v>
       </c>
       <c r="H3" s="5">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I3" s="5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J3" s="5">
         <v>0</v>
@@ -1758,34 +1914,52 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.4711362930647738</v>
+      </c>
+      <c r="O3" s="5">
+        <v>12</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.6601217691524652</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.6601187173946528</v>
+      </c>
+      <c r="R3" s="5">
+        <v>12</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.634656395863567</v>
+        <v>0.2760957285187032</v>
       </c>
       <c r="C4" s="4">
-        <v>0.6346554421893416</v>
+        <v>0.2051281206493311</v>
       </c>
       <c r="D4" s="4">
-        <v>0.6292601489534718</v>
+        <v>0.2052912315564754</v>
       </c>
       <c r="E4" s="4">
-        <v>75.7465986394558</v>
+        <v>76.70408163265306</v>
       </c>
       <c r="F4" s="4">
-        <v>78.18791946308725</v>
+        <v>81.89597315436242</v>
       </c>
       <c r="G4" s="5">
         <v>20</v>
       </c>
       <c r="H4" s="5">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I4" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J4" s="5">
         <v>2</v>
@@ -1799,91 +1973,141 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.1297706228397146</v>
+      </c>
+      <c r="O4" s="5">
+        <v>18</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2787810792055098</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2225308017279733</v>
+      </c>
+      <c r="R4" s="5">
+        <v>18</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2113363135686086</v>
+        <v>0.4362269755838497</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2113363135686086</v>
+        <v>0.3532435544475447</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1564025271763967</v>
+        <v>0.3430253383157833</v>
       </c>
       <c r="E5" s="4">
-        <v>79.79591836734694</v>
+        <v>76.78571428571429</v>
       </c>
       <c r="F5" s="4">
-        <v>80.80536912751678</v>
+        <v>79.74832214765101</v>
       </c>
       <c r="G5" s="5">
         <v>2</v>
       </c>
       <c r="H5" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4362269755838497</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3532435544475447</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.2072140094278438</v>
+        <v>0.05520396037536557</v>
       </c>
       <c r="C6" s="4">
-        <v>0.2998821385845076</v>
+        <v>0.05520396037536557</v>
       </c>
       <c r="D6" s="4">
-        <v>0.1689893123148067</v>
+        <v>0.06447702757213847</v>
       </c>
       <c r="E6" s="4">
-        <v>82.09183673469387</v>
+        <v>79.69387755102041</v>
       </c>
       <c r="F6" s="4">
-        <v>83.27181208053692</v>
+        <v>84.9496644295302</v>
       </c>
       <c r="G6" s="5">
         <v>2</v>
       </c>
       <c r="H6" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" s="5">
         <v>0</v>
       </c>
       <c r="J6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" s="5">
         <v>0</v>
       </c>
       <c r="L6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>2</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.05520396037536557</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.05520396037536557</v>
+      </c>
+      <c r="R6" s="5">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1894,6 +2118,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1901,7 +2126,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1912,9 +2137,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1948,8 +2179,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1971,40 +2210,58 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2681698680331465</v>
+        <v>0.193355597834185</v>
       </c>
       <c r="C3" s="4">
-        <v>0.252697510390135</v>
+        <v>0.193355597834185</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2518771052767989</v>
+        <v>0.1941080367245838</v>
       </c>
       <c r="E3" s="4">
-        <v>81.38945578231294</v>
+        <v>84.67346938775511</v>
       </c>
       <c r="F3" s="4">
-        <v>82.56655480984328</v>
+        <v>89.75838926174497</v>
       </c>
       <c r="G3" s="5">
         <v>20</v>
       </c>
       <c r="H3" s="5">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I3" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K3" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
         <v>0</v>
@@ -2012,25 +2269,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.002919056120803276</v>
+      </c>
+      <c r="O3" s="5">
+        <v>20</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.193355597834185</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.193355597834185</v>
+      </c>
+      <c r="R3" s="5">
+        <v>20</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.1301571344054537</v>
+        <v>0.07224944422220374</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1301571344054537</v>
+        <v>0.07224944422220374</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1088123130612075</v>
+        <v>0.05888918505003633</v>
       </c>
       <c r="E4" s="4">
-        <v>81.92346938775511</v>
+        <v>84.13265306122449</v>
       </c>
       <c r="F4" s="4">
-        <v>86.48545861297539</v>
+        <v>88.70469798657719</v>
       </c>
       <c r="G4" s="5">
         <v>20</v>
@@ -2053,91 +2328,141 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.06302054907877533</v>
+      </c>
+      <c r="O4" s="5">
+        <v>20</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.05247879080442373</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.05247879080442373</v>
+      </c>
+      <c r="R4" s="5">
+        <v>20</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.1811346400609182</v>
+        <v>0.1338592622536368</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1811346400609182</v>
+        <v>0.1914494735863315</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1621689189305471</v>
+        <v>0.1001460070696325</v>
       </c>
       <c r="E5" s="4">
-        <v>82.95918367346938</v>
+        <v>83.58843537414965</v>
       </c>
       <c r="F5" s="4">
-        <v>87.46085011185683</v>
+        <v>84.29530201342281</v>
       </c>
       <c r="G5" s="5">
         <v>2</v>
       </c>
       <c r="H5" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1338592622536368</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1914494735863315</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.0508643504617794</v>
+        <v>0.1254253699879833</v>
       </c>
       <c r="C6" s="4">
-        <v>0.0795104154094588</v>
+        <v>0.1254253699879833</v>
       </c>
       <c r="D6" s="4">
-        <v>0.04436261768205441</v>
+        <v>0.1126335797728153</v>
       </c>
       <c r="E6" s="4">
-        <v>77.55102040816327</v>
+        <v>87.09183673469387</v>
       </c>
       <c r="F6" s="4">
-        <v>81.86241610738254</v>
+        <v>90.06711409395973</v>
       </c>
       <c r="G6" s="5">
         <v>2</v>
       </c>
       <c r="H6" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" s="5">
         <v>0</v>
       </c>
       <c r="J6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" s="5">
         <v>0</v>
       </c>
       <c r="L6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>2</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.1254253699879833</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.1254253699879833</v>
+      </c>
+      <c r="R6" s="5">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2148,6 +2473,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2155,7 +2481,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2166,9 +2492,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2202,8 +2534,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2225,75 +2565,111 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.436772722445312</v>
+        <v>0.2710426463425392</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4369114820583491</v>
+        <v>0.2718191087832175</v>
       </c>
       <c r="D3" s="4">
-        <v>0.4383517210109858</v>
+        <v>0.2943340030811669</v>
       </c>
       <c r="E3" s="4">
-        <v>73.10544217687074</v>
+        <v>78.08503401360545</v>
       </c>
       <c r="F3" s="4">
-        <v>70.66946308724825</v>
+        <v>76.77069351230423</v>
       </c>
       <c r="G3" s="5">
         <v>20</v>
       </c>
       <c r="H3" s="5">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I3" s="5">
         <v>6</v>
       </c>
       <c r="J3" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.1549077861792674</v>
+      </c>
+      <c r="O3" s="5">
+        <v>14</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.271944070689746</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2711607741595279</v>
+      </c>
+      <c r="R3" s="5">
+        <v>14</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2934245322860079</v>
+        <v>0.634656395863567</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2736160353059758</v>
+        <v>0.6346554421893416</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2460941527999239</v>
+        <v>0.6292601489534718</v>
       </c>
       <c r="E4" s="4">
-        <v>76.5204081632653</v>
+        <v>75.7465986394558</v>
       </c>
       <c r="F4" s="4">
-        <v>81.35906040268456</v>
+        <v>78.18791946308725</v>
       </c>
       <c r="G4" s="5">
         <v>20</v>
       </c>
       <c r="H4" s="5">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" s="5">
         <v>2</v>
@@ -2307,91 +2683,141 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.4112620634437008</v>
+      </c>
+      <c r="O4" s="5">
+        <v>16</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.634656395863567</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.6346554421893416</v>
+      </c>
+      <c r="R4" s="5">
+        <v>16</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.6022750724187063</v>
+        <v>0.2072140094278438</v>
       </c>
       <c r="C5" s="4">
-        <v>0.6022750724187063</v>
+        <v>0.2998821385845076</v>
       </c>
       <c r="D5" s="4">
-        <v>0.5752765525212453</v>
+        <v>0.1689893123148067</v>
       </c>
       <c r="E5" s="4">
-        <v>81.83673469387755</v>
+        <v>82.09183673469387</v>
       </c>
       <c r="F5" s="4">
-        <v>87.04697986577182</v>
+        <v>83.27181208053692</v>
       </c>
       <c r="G5" s="5">
         <v>2</v>
       </c>
       <c r="H5" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2072140094278438</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2998821385845076</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.387836110257922</v>
+        <v>0.2113363135686086</v>
       </c>
       <c r="C6" s="4">
-        <v>0.4356472142681014</v>
+        <v>0.2113363135686086</v>
       </c>
       <c r="D6" s="4">
-        <v>0.3101917621133907</v>
+        <v>0.1564025271763967</v>
       </c>
       <c r="E6" s="4">
-        <v>79.03061224489795</v>
+        <v>79.79591836734694</v>
       </c>
       <c r="F6" s="4">
-        <v>81.05704697986577</v>
+        <v>80.80536912751678</v>
       </c>
       <c r="G6" s="5">
         <v>2</v>
       </c>
       <c r="H6" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" s="5">
         <v>0</v>
       </c>
       <c r="J6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" s="5">
         <v>0</v>
       </c>
       <c r="L6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>2</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.2113363135686086</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.2113363135686086</v>
+      </c>
+      <c r="R6" s="5">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2402,6 +2828,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2409,7 +2836,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2420,9 +2847,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2456,8 +2889,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2479,40 +2920,58 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.07375102428195106</v>
+        <v>0.2681698680331465</v>
       </c>
       <c r="C3" s="4">
-        <v>0.07375102428195106</v>
+        <v>0.252697510390135</v>
       </c>
       <c r="D3" s="4">
-        <v>0.06878748325106657</v>
+        <v>0.2518771052767989</v>
       </c>
       <c r="E3" s="4">
-        <v>99.51020408163265</v>
+        <v>81.38945578231294</v>
       </c>
       <c r="F3" s="4">
-        <v>99.23825503355705</v>
+        <v>82.56655480984328</v>
       </c>
       <c r="G3" s="5">
         <v>20</v>
       </c>
       <c r="H3" s="5">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K3" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L3" s="5">
         <v>0</v>
@@ -2520,25 +2979,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.07299230359785724</v>
+      </c>
+      <c r="O3" s="5">
+        <v>16</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.253571407313575</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2435734724404028</v>
+      </c>
+      <c r="R3" s="5">
+        <v>16</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.1610849288321332</v>
+        <v>0.1301571344054537</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1610849288321332</v>
+        <v>0.1301571344054537</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1572755356348308</v>
+        <v>0.1088123130612075</v>
       </c>
       <c r="E4" s="4">
-        <v>99.48979591836735</v>
+        <v>81.92346938775511</v>
       </c>
       <c r="F4" s="4">
-        <v>99.21476510067114</v>
+        <v>86.48545861297539</v>
       </c>
       <c r="G4" s="5">
         <v>20</v>
@@ -2561,66 +3038,100 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.1301571344054537</v>
+      </c>
+      <c r="O4" s="5">
+        <v>20</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.04020372320723253</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.04020372320723253</v>
+      </c>
+      <c r="R4" s="5">
+        <v>20</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.1347662944426489</v>
+        <v>0.0508643504617794</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1347662944426489</v>
+        <v>0.0795104154094588</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1298246521582556</v>
+        <v>0.04436261768205441</v>
       </c>
       <c r="E5" s="4">
-        <v>99.48979591836735</v>
+        <v>77.55102040816327</v>
       </c>
       <c r="F5" s="4">
-        <v>98.8255033557047</v>
+        <v>81.86241610738254</v>
       </c>
       <c r="G5" s="5">
         <v>2</v>
       </c>
       <c r="H5" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.0508643504617794</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.0795104154094588</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.01732179191094474</v>
+        <v>0.1811346400609182</v>
       </c>
       <c r="C6" s="4">
-        <v>0.01732179191094474</v>
+        <v>0.1811346400609182</v>
       </c>
       <c r="D6" s="4">
-        <v>0.009772401714144507</v>
+        <v>0.1621689189305471</v>
       </c>
       <c r="E6" s="4">
-        <v>98.87755102040816</v>
+        <v>82.95918367346938</v>
       </c>
       <c r="F6" s="4">
-        <v>98.08724832214764</v>
+        <v>87.46085011185683</v>
       </c>
       <c r="G6" s="5">
         <v>2</v>
@@ -2643,9 +3154,25 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>2</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.1811346400609182</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.1811346400609182</v>
+      </c>
+      <c r="R6" s="5">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2656,6 +3183,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2663,7 +3191,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2674,9 +3202,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2710,8 +3244,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2733,148 +3275,218 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4053781765054694</v>
+        <v>0.436772722445312</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4053781765054694</v>
+        <v>0.4369114820583491</v>
       </c>
       <c r="D3" s="4">
-        <v>0.4335708965532746</v>
+        <v>0.4383517210109858</v>
       </c>
       <c r="E3" s="4">
-        <v>76.8860544217687</v>
+        <v>73.10544217687074</v>
       </c>
       <c r="F3" s="4">
-        <v>81.15156599552566</v>
+        <v>70.66946308724825</v>
       </c>
       <c r="G3" s="5">
         <v>20</v>
       </c>
       <c r="H3" s="5">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J3" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.08684748467082197</v>
+      </c>
+      <c r="O3" s="5">
+        <v>12</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.436772722445312</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.4369114820583491</v>
+      </c>
+      <c r="R3" s="5">
+        <v>12</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3284819963286269</v>
+        <v>0.2934245322860079</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3284819963286269</v>
+        <v>0.2736160353059758</v>
       </c>
       <c r="D4" s="4">
-        <v>0.329431783508335</v>
+        <v>0.2460941527999239</v>
       </c>
       <c r="E4" s="4">
-        <v>77.29591836734694</v>
+        <v>76.5204081632653</v>
       </c>
       <c r="F4" s="4">
-        <v>84.42953020134229</v>
+        <v>81.35906040268456</v>
       </c>
       <c r="G4" s="5">
         <v>20</v>
       </c>
       <c r="H4" s="5">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.2736160353059758</v>
+      </c>
+      <c r="O4" s="5">
+        <v>18</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.06178631474031136</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.04664201973364358</v>
+      </c>
+      <c r="R4" s="5">
+        <v>18</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.5276900518765615</v>
+        <v>0.387836110257922</v>
       </c>
       <c r="C5" s="4">
-        <v>0.5276900518765615</v>
+        <v>0.4356472142681014</v>
       </c>
       <c r="D5" s="4">
-        <v>0.5203659225335286</v>
+        <v>0.3101917621133907</v>
       </c>
       <c r="E5" s="4">
-        <v>83.31632653061224</v>
+        <v>79.03061224489795</v>
       </c>
       <c r="F5" s="4">
-        <v>88.55704697986577</v>
+        <v>81.05704697986577</v>
       </c>
       <c r="G5" s="5">
         <v>2</v>
       </c>
       <c r="H5" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.387836110257922</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4356472142681014</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.2823439952371487</v>
+        <v>0.6022750724187063</v>
       </c>
       <c r="C6" s="4">
-        <v>0.2823439952371487</v>
+        <v>0.6022750724187063</v>
       </c>
       <c r="D6" s="4">
-        <v>0.2619741674898037</v>
+        <v>0.5752765525212453</v>
       </c>
       <c r="E6" s="4">
-        <v>83.46938775510205</v>
+        <v>81.83673469387755</v>
       </c>
       <c r="F6" s="4">
-        <v>89.81543624161074</v>
+        <v>87.04697986577182</v>
       </c>
       <c r="G6" s="5">
         <v>2</v>
@@ -2897,9 +3509,25 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>2</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.6022750724187063</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.6022750724187063</v>
+      </c>
+      <c r="R6" s="5">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2910,6 +3538,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2917,7 +3546,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2928,9 +3557,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2964,8 +3599,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2987,34 +3630,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.08941037145849293</v>
+        <v>0.07375102428195106</v>
       </c>
       <c r="C3" s="4">
-        <v>0.0784478544131291</v>
+        <v>0.07375102428195106</v>
       </c>
       <c r="D3" s="4">
-        <v>0.06654451874491726</v>
+        <v>0.06878748325106657</v>
       </c>
       <c r="E3" s="4">
-        <v>96.4795918367347</v>
+        <v>99.51020408163265</v>
       </c>
       <c r="F3" s="4">
-        <v>94.31543624161074</v>
+        <v>99.23825503355705</v>
       </c>
       <c r="G3" s="5">
         <v>20</v>
       </c>
       <c r="H3" s="5">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I3" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
         <v>0</v>
@@ -3028,25 +3689,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.07375102428195106</v>
+      </c>
+      <c r="O3" s="5">
+        <v>20</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.02421985141045866</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.02421985141045866</v>
+      </c>
+      <c r="R3" s="5">
+        <v>20</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.1098028098262076</v>
+        <v>0.1610849288321332</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1098028098262076</v>
+        <v>0.1610849288321332</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1037516077078151</v>
+        <v>0.1572755356348308</v>
       </c>
       <c r="E4" s="4">
-        <v>99.15306122448979</v>
+        <v>99.48979591836735</v>
       </c>
       <c r="F4" s="4">
-        <v>98.79865771812081</v>
+        <v>99.21476510067114</v>
       </c>
       <c r="G4" s="5">
         <v>20</v>
@@ -3069,25 +3748,43 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.1610849288321332</v>
+      </c>
+      <c r="O4" s="5">
+        <v>20</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.07144129117222983</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.07144129117222983</v>
+      </c>
+      <c r="R4" s="5">
+        <v>20</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.1171042908062887</v>
+        <v>0.01732179191094474</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1171042908062887</v>
+        <v>0.01732179191094474</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1103380460371923</v>
+        <v>0.009772401714144507</v>
       </c>
       <c r="E5" s="4">
-        <v>99.59183673469387</v>
+        <v>98.87755102040816</v>
       </c>
       <c r="F5" s="4">
-        <v>98.94295302013423</v>
+        <v>98.08724832214764</v>
       </c>
       <c r="G5" s="5">
         <v>2</v>
@@ -3110,25 +3807,41 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.01732179191094474</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.01732179191094474</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.01211677307946957</v>
+        <v>0.1347662944426489</v>
       </c>
       <c r="C6" s="4">
-        <v>0.01211677307946957</v>
+        <v>0.1347662944426489</v>
       </c>
       <c r="D6" s="4">
-        <v>0.01142890567643917</v>
+        <v>0.1298246521582556</v>
       </c>
       <c r="E6" s="4">
-        <v>98.62244897959184</v>
+        <v>99.48979591836735</v>
       </c>
       <c r="F6" s="4">
-        <v>98.05369127516778</v>
+        <v>98.8255033557047</v>
       </c>
       <c r="G6" s="5">
         <v>2</v>
@@ -3151,9 +3864,25 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>2</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.1347662944426489</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.1347662944426489</v>
+      </c>
+      <c r="R6" s="5">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3164,6 +3893,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3171,7 +3901,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3182,9 +3912,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3218,8 +3954,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3241,34 +3985,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.7935870551824238</v>
+        <v>0.4053781765054694</v>
       </c>
       <c r="C3" s="4">
-        <v>0.902750490601635</v>
+        <v>0.4053781765054694</v>
       </c>
       <c r="D3" s="4">
-        <v>0.7397054502020097</v>
+        <v>0.4335708965532746</v>
       </c>
       <c r="E3" s="4">
-        <v>74.84523809523805</v>
+        <v>76.8860544217687</v>
       </c>
       <c r="F3" s="4">
-        <v>79.99328859060383</v>
+        <v>81.15156599552566</v>
       </c>
       <c r="G3" s="5">
         <v>20</v>
       </c>
       <c r="H3" s="5">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I3" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
         <v>0</v>
@@ -3282,25 +4044,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.3731938422977649</v>
+      </c>
+      <c r="O3" s="5">
+        <v>20</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1840088869428985</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1840088869428985</v>
+      </c>
+      <c r="R3" s="5">
+        <v>20</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.5520360668218898</v>
+        <v>0.3284819963286269</v>
       </c>
       <c r="C4" s="4">
-        <v>0.5520360668218898</v>
+        <v>0.3284819963286269</v>
       </c>
       <c r="D4" s="4">
-        <v>0.5448204194224642</v>
+        <v>0.329431783508335</v>
       </c>
       <c r="E4" s="4">
-        <v>76.94897959183673</v>
+        <v>77.29591836734694</v>
       </c>
       <c r="F4" s="4">
-        <v>85.51118568232661</v>
+        <v>84.42953020134229</v>
       </c>
       <c r="G4" s="5">
         <v>20</v>
@@ -3323,25 +4103,43 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.1960027177847193</v>
+      </c>
+      <c r="O4" s="5">
+        <v>20</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3281379112115234</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3281379112115234</v>
+      </c>
+      <c r="R4" s="5">
+        <v>20</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.3275635082354711</v>
+        <v>0.2823439952371487</v>
       </c>
       <c r="C5" s="4">
-        <v>0.3275635082354711</v>
+        <v>0.2823439952371487</v>
       </c>
       <c r="D5" s="4">
-        <v>0.3019472349515127</v>
+        <v>0.2619741674898037</v>
       </c>
       <c r="E5" s="4">
-        <v>84.28571428571429</v>
+        <v>83.46938775510205</v>
       </c>
       <c r="F5" s="4">
-        <v>89.63087248322148</v>
+        <v>89.81543624161074</v>
       </c>
       <c r="G5" s="5">
         <v>2</v>
@@ -3364,25 +4162,41 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2823439952371487</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2823439952371487</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.0467752400400272</v>
+        <v>0.5276900518765615</v>
       </c>
       <c r="C6" s="4">
-        <v>0.0467752400400272</v>
+        <v>0.5276900518765615</v>
       </c>
       <c r="D6" s="4">
-        <v>0.0794571522237888</v>
+        <v>0.5203659225335286</v>
       </c>
       <c r="E6" s="4">
-        <v>79.33673469387755</v>
+        <v>83.31632653061224</v>
       </c>
       <c r="F6" s="4">
-        <v>83.7751677852349</v>
+        <v>88.55704697986577</v>
       </c>
       <c r="G6" s="5">
         <v>2</v>
@@ -3405,9 +4219,25 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>2</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.5276900518765615</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.5276900518765615</v>
+      </c>
+      <c r="R6" s="5">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3418,12 +4248,1580 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.08941037145849293</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.0784478544131291</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.06654451874491726</v>
+      </c>
+      <c r="E3" s="4">
+        <v>96.4795918367347</v>
+      </c>
+      <c r="F3" s="4">
+        <v>94.31543624161074</v>
+      </c>
+      <c r="G3" s="5">
+        <v>20</v>
+      </c>
+      <c r="H3" s="5">
+        <v>18</v>
+      </c>
+      <c r="I3" s="5">
+        <v>2</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.0784478544131291</v>
+      </c>
+      <c r="O3" s="5">
+        <v>18</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.02834596981558046</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.01931494752246291</v>
+      </c>
+      <c r="R3" s="5">
+        <v>18</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.1098028098262076</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.1098028098262076</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.1037516077078151</v>
+      </c>
+      <c r="E4" s="4">
+        <v>99.15306122448979</v>
+      </c>
+      <c r="F4" s="4">
+        <v>98.79865771812081</v>
+      </c>
+      <c r="G4" s="5">
+        <v>20</v>
+      </c>
+      <c r="H4" s="5">
+        <v>20</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.1098028098262076</v>
+      </c>
+      <c r="O4" s="5">
+        <v>20</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.06226985817048027</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.06226985817048027</v>
+      </c>
+      <c r="R4" s="5">
+        <v>20</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.01211677307946957</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.01211677307946957</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.01142890567643917</v>
+      </c>
+      <c r="E5" s="4">
+        <v>98.62244897959184</v>
+      </c>
+      <c r="F5" s="4">
+        <v>98.05369127516778</v>
+      </c>
+      <c r="G5" s="5">
+        <v>2</v>
+      </c>
+      <c r="H5" s="5">
+        <v>2</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.01211677307946957</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.01211677307946957</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="4">
+        <v>0.1171042908062887</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0.1171042908062887</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0.1103380460371923</v>
+      </c>
+      <c r="E6" s="4">
+        <v>99.59183673469387</v>
+      </c>
+      <c r="F6" s="4">
+        <v>98.94295302013423</v>
+      </c>
+      <c r="G6" s="5">
+        <v>2</v>
+      </c>
+      <c r="H6" s="5">
+        <v>2</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>2</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.1171042908062887</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.1171042908062887</v>
+      </c>
+      <c r="R6" s="5">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.7935870551824238</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.902750490601635</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.7397054502020097</v>
+      </c>
+      <c r="E3" s="4">
+        <v>74.84523809523805</v>
+      </c>
+      <c r="F3" s="4">
+        <v>79.99328859060383</v>
+      </c>
+      <c r="G3" s="5">
+        <v>20</v>
+      </c>
+      <c r="H3" s="5">
+        <v>16</v>
+      </c>
+      <c r="I3" s="5">
+        <v>4</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.902750490601635</v>
+      </c>
+      <c r="O3" s="5">
+        <v>16</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1751227406190072</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.08244913149974487</v>
+      </c>
+      <c r="R3" s="5">
+        <v>16</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.5520360668218898</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.5520360668218898</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.5448204194224642</v>
+      </c>
+      <c r="E4" s="4">
+        <v>76.94897959183673</v>
+      </c>
+      <c r="F4" s="4">
+        <v>85.51118568232661</v>
+      </c>
+      <c r="G4" s="5">
+        <v>20</v>
+      </c>
+      <c r="H4" s="5">
+        <v>20</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.5520360668218898</v>
+      </c>
+      <c r="O4" s="5">
+        <v>20</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.04490845520238858</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.04490845520238858</v>
+      </c>
+      <c r="R4" s="5">
+        <v>20</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.0467752400400272</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.0467752400400272</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.0794571522237888</v>
+      </c>
+      <c r="E5" s="4">
+        <v>79.33673469387755</v>
+      </c>
+      <c r="F5" s="4">
+        <v>83.7751677852349</v>
+      </c>
+      <c r="G5" s="5">
+        <v>2</v>
+      </c>
+      <c r="H5" s="5">
+        <v>2</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.0467752400400272</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.0467752400400272</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="4">
+        <v>0.3275635082354711</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0.3275635082354711</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0.3019472349515127</v>
+      </c>
+      <c r="E6" s="4">
+        <v>84.28571428571429</v>
+      </c>
+      <c r="F6" s="4">
+        <v>89.63087248322148</v>
+      </c>
+      <c r="G6" s="5">
+        <v>2</v>
+      </c>
+      <c r="H6" s="5">
+        <v>2</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>2</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.3275635082354711</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.3275635082354711</v>
+      </c>
+      <c r="R6" s="5">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>88.63636363636364</v>
+      </c>
+      <c r="C3" s="3">
+        <v>9.090909090909092</v>
+      </c>
+      <c r="D3" s="3">
+        <v>2.272727272727273</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>2.272727272727273</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.3599549377728677</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.3276457334354815</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.355761315665396</v>
+      </c>
+      <c r="K3" s="4">
+        <v>75.19867037724153</v>
+      </c>
+      <c r="L3" s="4">
+        <v>80.41946308724791</v>
+      </c>
+      <c r="M3" s="5">
+        <v>44</v>
+      </c>
+      <c r="N3" s="5">
+        <v>222049.6356487274</v>
+      </c>
+      <c r="O3" s="4">
+        <v>33.43617461959455</v>
+      </c>
+      <c r="P3" s="5">
+        <v>6641</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>95.45454545454545</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3">
+        <v>4.545454545454546</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>4.545454545454546</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.3100930322523948</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.3090278244371928</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.3039036996342474</v>
+      </c>
+      <c r="K4" s="4">
+        <v>71.66589363017921</v>
+      </c>
+      <c r="L4" s="4">
+        <v>78.00132194427485</v>
+      </c>
+      <c r="M4" s="5">
+        <v>44</v>
+      </c>
+      <c r="N4" s="5">
+        <v>283673.629283905</v>
+      </c>
+      <c r="O4" s="4">
+        <v>48.79986741508774</v>
+      </c>
+      <c r="P4" s="5">
+        <v>5813</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>93.18181818181817</v>
+      </c>
+      <c r="C5" s="3">
+        <v>4.545454545454546</v>
+      </c>
+      <c r="D5" s="3">
+        <v>2.272727272727273</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>2.272727272727273</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.1835500697338747</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.1799702331737868</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.1835430060814866</v>
+      </c>
+      <c r="K5" s="4">
+        <v>76.40769944341376</v>
+      </c>
+      <c r="L5" s="4">
+        <v>83.73296725645969</v>
+      </c>
+      <c r="M5" s="5">
+        <v>44</v>
+      </c>
+      <c r="N5" s="5">
+        <v>745647.2742557526</v>
+      </c>
+      <c r="O5" s="4">
+        <v>153.9321375424757</v>
+      </c>
+      <c r="P5" s="5">
+        <v>4844</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>84.09090909090909</v>
+      </c>
+      <c r="C6" s="3">
+        <v>13.63636363636363</v>
+      </c>
+      <c r="D6" s="3">
+        <v>2.272727272727273</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>2.272727272727273</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.2223884130568206</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.1991386147097624</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.1960557122530107</v>
+      </c>
+      <c r="K6" s="4">
+        <v>77.79993815708099</v>
+      </c>
+      <c r="L6" s="4">
+        <v>79.88534675615215</v>
+      </c>
+      <c r="M6" s="5">
+        <v>44</v>
+      </c>
+      <c r="N6" s="5">
+        <v>563017.4014568329</v>
+      </c>
+      <c r="O6" s="4">
+        <v>84.33454185992105</v>
+      </c>
+      <c r="P6" s="5">
+        <v>6676</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>100</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.140576379627336</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.140576379627336</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.1394942020526453</v>
+      </c>
+      <c r="K7" s="4">
+        <v>82.23252937538638</v>
+      </c>
+      <c r="L7" s="4">
+        <v>87.83251982916404</v>
+      </c>
+      <c r="M7" s="5">
+        <v>44</v>
+      </c>
+      <c r="N7" s="5">
+        <v>668474.5712280273</v>
+      </c>
+      <c r="O7" s="4">
+        <v>163.1619651520691</v>
+      </c>
+      <c r="P7" s="5">
+        <v>4097</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>93.18181818181817</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3">
+        <v>6.818181818181817</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>6.818181818181817</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.2223260493333208</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.2166735287538777</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.2212269067087045</v>
+      </c>
+      <c r="K8" s="4">
+        <v>80.34090909090881</v>
+      </c>
+      <c r="L8" s="4">
+        <v>84.95805369127726</v>
+      </c>
+      <c r="M8" s="5">
+        <v>44</v>
+      </c>
+      <c r="N8" s="5">
+        <v>58950.68311691284</v>
+      </c>
+      <c r="O8" s="4">
+        <v>12.73507952406845</v>
+      </c>
+      <c r="P8" s="5">
+        <v>4629</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>75</v>
+      </c>
+      <c r="C9" s="3">
+        <v>18.18181818181818</v>
+      </c>
+      <c r="D9" s="3">
+        <v>6.818181818181817</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>6.818181818181817</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.4491117917972257</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.3754736519708372</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.4233965930943668</v>
+      </c>
+      <c r="K9" s="4">
+        <v>77.43738404452662</v>
+      </c>
+      <c r="L9" s="4">
+        <v>80.33328248932335</v>
+      </c>
+      <c r="M9" s="5">
+        <v>44</v>
+      </c>
+      <c r="N9" s="5">
+        <v>195697.7372169495</v>
+      </c>
+      <c r="O9" s="4">
+        <v>32.8131685474429</v>
+      </c>
+      <c r="P9" s="5">
+        <v>5964</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>97.72727272727273</v>
+      </c>
+      <c r="C10" s="3">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3">
+        <v>2.272727272727273</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>2.272727272727273</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.1235285690285322</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.1246276275891738</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.1211860805790805</v>
+      </c>
+      <c r="K10" s="4">
+        <v>84.48824984539266</v>
+      </c>
+      <c r="L10" s="4">
+        <v>89.04514948139122</v>
+      </c>
+      <c r="M10" s="5">
+        <v>44</v>
+      </c>
+      <c r="N10" s="5">
+        <v>349478.6887168884</v>
+      </c>
+      <c r="O10" s="4">
+        <v>84.59905318733682</v>
+      </c>
+      <c r="P10" s="5">
+        <v>4131</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>75</v>
+      </c>
+      <c r="C11" s="3">
+        <v>18.18181818181818</v>
+      </c>
+      <c r="D11" s="3">
+        <v>6.818181818181817</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3">
+        <v>6.818181818181817</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.4311161358422538</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.4446452326965025</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0.4265318754944207</v>
+      </c>
+      <c r="K11" s="4">
+        <v>77.28200371057486</v>
+      </c>
+      <c r="L11" s="4">
+        <v>77.89378686190813</v>
+      </c>
+      <c r="M11" s="5">
+        <v>44</v>
+      </c>
+      <c r="N11" s="5">
+        <v>251826.7476558685</v>
+      </c>
+      <c r="O11" s="4">
+        <v>42.64635862080754</v>
+      </c>
+      <c r="P11" s="5">
+        <v>5905</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>88.63636363636364</v>
+      </c>
+      <c r="C12" s="3">
+        <v>4.545454545454546</v>
+      </c>
+      <c r="D12" s="3">
+        <v>6.818181818181817</v>
+      </c>
+      <c r="E12" s="3">
+        <v>4.545454545454546</v>
+      </c>
+      <c r="F12" s="3">
+        <v>2.272727272727273</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.1440795588968533</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.1318725568903177</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.1394077549714315</v>
+      </c>
+      <c r="K12" s="4">
+        <v>81.52906617192339</v>
+      </c>
+      <c r="L12" s="4">
+        <v>84.5383363839743</v>
+      </c>
+      <c r="M12" s="5">
+        <v>44</v>
+      </c>
+      <c r="N12" s="5">
+        <v>181076.6146183014</v>
+      </c>
+      <c r="O12" s="4">
+        <v>18.98674788909525</v>
+      </c>
+      <c r="P12" s="5">
+        <v>9537</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>75</v>
+      </c>
+      <c r="C13" s="3">
+        <v>13.63636363636363</v>
+      </c>
+      <c r="D13" s="3">
+        <v>11.36363636363636</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>11.36363636363636</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.2716227979333119</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.2340209545154935</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0.2676605714193533</v>
+      </c>
+      <c r="K13" s="4">
+        <v>75.3239022881877</v>
+      </c>
+      <c r="L13" s="4">
+        <v>76.74496644295282</v>
+      </c>
+      <c r="M13" s="5">
+        <v>44</v>
+      </c>
+      <c r="N13" s="5">
+        <v>503243.5042858124</v>
+      </c>
+      <c r="O13" s="4">
+        <v>77.20827006532868</v>
+      </c>
+      <c r="P13" s="5">
+        <v>6518</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>100</v>
+      </c>
+      <c r="C14" s="3">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.05039543237183994</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.05039543237183994</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.04872629048146719</v>
+      </c>
+      <c r="K14" s="4">
+        <v>99.4712430426716</v>
+      </c>
+      <c r="L14" s="4">
+        <v>99.15649786455155</v>
+      </c>
+      <c r="M14" s="5">
+        <v>44</v>
+      </c>
+      <c r="N14" s="5">
+        <v>212763.5855674744</v>
+      </c>
+      <c r="O14" s="4">
+        <v>228.7780489972843</v>
+      </c>
+      <c r="P14" s="5">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>100</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.2696137285753604</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.2696137285753604</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.2838242703926354</v>
+      </c>
+      <c r="K15" s="4">
+        <v>77.66388373531221</v>
+      </c>
+      <c r="L15" s="4">
+        <v>83.37197478137163</v>
+      </c>
+      <c r="M15" s="5">
+        <v>44</v>
+      </c>
+      <c r="N15" s="5">
+        <v>1208461.856365204</v>
+      </c>
+      <c r="O15" s="4">
+        <v>229.8767084582849</v>
+      </c>
+      <c r="P15" s="5">
+        <v>5257</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>95.45454545454545</v>
+      </c>
+      <c r="C16" s="3">
+        <v>4.545454545454546</v>
+      </c>
+      <c r="D16" s="3">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.04706269744301661</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.04408353206155843</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.04434951652023793</v>
+      </c>
+      <c r="K16" s="4">
+        <v>97.93367346938749</v>
+      </c>
+      <c r="L16" s="4">
+        <v>96.73352654057554</v>
+      </c>
+      <c r="M16" s="5">
+        <v>44</v>
+      </c>
+      <c r="N16" s="5">
+        <v>120216.3820266724</v>
+      </c>
+      <c r="O16" s="4">
+        <v>98.94352430178795</v>
+      </c>
+      <c r="P16" s="5">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>90.90909090909091</v>
+      </c>
+      <c r="C17" s="3">
+        <v>9.090909090909092</v>
+      </c>
+      <c r="D17" s="3">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.1170295775677025</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.07415081761486715</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0.1481312150508861</v>
+      </c>
+      <c r="K17" s="4">
+        <v>76.43475572046967</v>
+      </c>
+      <c r="L17" s="4">
+        <v>83.11139922717098</v>
+      </c>
+      <c r="M17" s="5">
+        <v>44</v>
+      </c>
+      <c r="N17" s="5">
+        <v>502615.8752441406</v>
+      </c>
+      <c r="O17" s="4">
+        <v>98.28233774816985</v>
+      </c>
+      <c r="P17" s="5">
+        <v>5114</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3933,7 +6331,7 @@
         <v>0</v>
       </c>
       <c r="K12" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L12" s="5">
         <v>1</v>
@@ -4178,9 +6576,764 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>39</v>
+      </c>
+      <c r="C3" s="5">
+        <v>4</v>
+      </c>
+      <c r="D3" s="5">
+        <v>1</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5">
+        <v>1</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>1</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>42</v>
+      </c>
+      <c r="C4" s="5">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5">
+        <v>2</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5">
+        <v>2</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>2</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>41</v>
+      </c>
+      <c r="C5" s="5">
+        <v>2</v>
+      </c>
+      <c r="D5" s="5">
+        <v>1</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>1</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>1</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>37</v>
+      </c>
+      <c r="C6" s="5">
+        <v>6</v>
+      </c>
+      <c r="D6" s="5">
+        <v>1</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>1</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>1</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>44</v>
+      </c>
+      <c r="C7" s="5">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5">
+        <v>0</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>0</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>41</v>
+      </c>
+      <c r="C8" s="5">
+        <v>0</v>
+      </c>
+      <c r="D8" s="5">
+        <v>3</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>3</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>3</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>33</v>
+      </c>
+      <c r="C9" s="5">
+        <v>8</v>
+      </c>
+      <c r="D9" s="5">
+        <v>3</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5">
+        <v>3</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>3</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>43</v>
+      </c>
+      <c r="C10" s="5">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5">
+        <v>1</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5">
+        <v>1</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>1</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>33</v>
+      </c>
+      <c r="C11" s="5">
+        <v>8</v>
+      </c>
+      <c r="D11" s="5">
+        <v>3</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5">
+        <v>3</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>3</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>39</v>
+      </c>
+      <c r="C12" s="5">
+        <v>2</v>
+      </c>
+      <c r="D12" s="5">
+        <v>3</v>
+      </c>
+      <c r="E12" s="5">
+        <v>2</v>
+      </c>
+      <c r="F12" s="5">
+        <v>1</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>2</v>
+      </c>
+      <c r="I12" s="5">
+        <v>2</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>1</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>33</v>
+      </c>
+      <c r="C13" s="5">
+        <v>6</v>
+      </c>
+      <c r="D13" s="5">
+        <v>5</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5">
+        <v>5</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>5</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>44</v>
+      </c>
+      <c r="C14" s="5">
+        <v>0</v>
+      </c>
+      <c r="D14" s="5">
+        <v>0</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5">
+        <v>0</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <v>0</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>44</v>
+      </c>
+      <c r="C15" s="5">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5">
+        <v>0</v>
+      </c>
+      <c r="E15" s="5">
+        <v>0</v>
+      </c>
+      <c r="F15" s="5">
+        <v>0</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>0</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>42</v>
+      </c>
+      <c r="C16" s="5">
+        <v>2</v>
+      </c>
+      <c r="D16" s="5">
+        <v>0</v>
+      </c>
+      <c r="E16" s="5">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5">
+        <v>0</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5">
+        <v>0</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>0</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>40</v>
+      </c>
+      <c r="C17" s="5">
+        <v>4</v>
+      </c>
+      <c r="D17" s="5">
+        <v>0</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5">
+        <v>0</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>0</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4191,9 +7344,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4227,8 +7386,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4250,10 +7417,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.6166171495540766</v>
@@ -4291,10 +7476,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.2467236429411059</v>
+      </c>
+      <c r="O3" s="5">
+        <v>16</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.6166171495540766</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.6166100685222773</v>
+      </c>
+      <c r="R3" s="5">
+        <v>16</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.08731693241643371</v>
@@ -4332,91 +7535,141 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.03865451561578084</v>
+      </c>
+      <c r="O4" s="5">
+        <v>20</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.08034995829279068</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.08034995829279068</v>
+      </c>
+      <c r="R4" s="5">
+        <v>20</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
+        <v>0.5795842525003536</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.5659167417034041</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.4652139064310177</v>
+      </c>
+      <c r="E5" s="4">
+        <v>80.71428571428571</v>
+      </c>
+      <c r="F5" s="4">
+        <v>78.52348993288591</v>
+      </c>
+      <c r="G5" s="5">
+        <v>2</v>
+      </c>
+      <c r="H5" s="5">
+        <v>1</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>1</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>1</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.5795842525003536</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.5659167417034041</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="4">
         <v>0.3697533000340627</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C6" s="4">
         <v>0.3697533000340627</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D6" s="4">
         <v>0.316906868301885</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E6" s="4">
         <v>78.0952380952381</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F6" s="4">
         <v>83.38926174496645</v>
       </c>
-      <c r="G5" s="5">
-        <v>2</v>
-      </c>
-      <c r="H5" s="5">
-        <v>2</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" s="4">
-        <v>0.5795842525003536</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0.5659167417034041</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0.4652139064310177</v>
-      </c>
-      <c r="E6" s="4">
-        <v>80.71428571428571</v>
-      </c>
-      <c r="F6" s="4">
-        <v>78.52348993288591</v>
-      </c>
       <c r="G6" s="5">
         <v>2</v>
       </c>
       <c r="H6" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" s="5">
         <v>0</v>
       </c>
       <c r="J6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" s="5">
         <v>0</v>
       </c>
       <c r="L6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>2</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.3697533000340627</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.3697533000340627</v>
+      </c>
+      <c r="R6" s="5">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4427,14 +7680,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4445,9 +7699,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4481,8 +7741,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4504,10 +7772,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.4023172040615464</v>
@@ -4545,10 +7831,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.04198092905280646</v>
+      </c>
+      <c r="O3" s="5">
+        <v>20</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4038421182862657</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.4038421182862657</v>
+      </c>
+      <c r="R3" s="5">
+        <v>20</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.2217403415961599</v>
@@ -4586,67 +7890,101 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.122591031448893</v>
+      </c>
+      <c r="O4" s="5">
+        <v>18</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1843790385044283</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1679253320747384</v>
+      </c>
+      <c r="R4" s="5">
+        <v>18</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
+        <v>0.629410874509631</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.629410874509631</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.6410800334451778</v>
+      </c>
+      <c r="E5" s="4">
+        <v>71.78571428571429</v>
+      </c>
+      <c r="F5" s="4">
+        <v>79.61409395973155</v>
+      </c>
+      <c r="G5" s="5">
+        <v>2</v>
+      </c>
+      <c r="H5" s="5">
+        <v>2</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.629410874509631</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.629410874509631</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="4">
         <v>0.3104242671361135</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C6" s="4">
         <v>0.3104242671361135</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D6" s="4">
         <v>0.2900652278294729</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E6" s="4">
         <v>68.9795918367347</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F6" s="4">
         <v>72.57270693512304</v>
       </c>
-      <c r="G5" s="5">
-        <v>2</v>
-      </c>
-      <c r="H5" s="5">
-        <v>2</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" s="4">
-        <v>0.629410874509631</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0.629410874509631</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0.6410800334451778</v>
-      </c>
-      <c r="E6" s="4">
-        <v>71.78571428571429</v>
-      </c>
-      <c r="F6" s="4">
-        <v>79.61409395973155</v>
-      </c>
       <c r="G6" s="5">
         <v>2</v>
       </c>
@@ -4668,9 +8006,25 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>2</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.3104242671361135</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.3104242671361135</v>
+      </c>
+      <c r="R6" s="5">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4681,14 +8035,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4699,9 +8054,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4735,8 +8096,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4758,10 +8127,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.250114778909483</v>
@@ -4799,10 +8186,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.07045535815187678</v>
+      </c>
+      <c r="O3" s="5">
+        <v>18</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2486183007895306</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2493411147370352</v>
+      </c>
+      <c r="R3" s="5">
+        <v>18</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.3574975137627917</v>
@@ -4840,91 +8245,141 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.3574975137627917</v>
+      </c>
+      <c r="O4" s="5">
+        <v>20</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.09366816858062521</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.09366816858062521</v>
+      </c>
+      <c r="R4" s="5">
+        <v>20</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
+        <v>0.2703880671797378</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.3275785767182242</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.231023189091502</v>
+      </c>
+      <c r="E5" s="4">
+        <v>81.17346938775511</v>
+      </c>
+      <c r="F5" s="4">
+        <v>84.81543624161074</v>
+      </c>
+      <c r="G5" s="5">
+        <v>2</v>
+      </c>
+      <c r="H5" s="5">
+        <v>1</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>1</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>1</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2703880671797378</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3275785767182242</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="4">
         <v>0.3448487732639478</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C6" s="4">
         <v>0.3448487732639478</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D6" s="4">
         <v>0.309157824896829</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E6" s="4">
         <v>79.84693877551021</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F6" s="4">
         <v>85.41946308724832</v>
       </c>
-      <c r="G5" s="5">
-        <v>2</v>
-      </c>
-      <c r="H5" s="5">
-        <v>2</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" s="4">
-        <v>0.2703880671797378</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0.3275785767182242</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0.231023189091502</v>
-      </c>
-      <c r="E6" s="4">
-        <v>81.17346938775511</v>
-      </c>
-      <c r="F6" s="4">
-        <v>84.81543624161074</v>
-      </c>
       <c r="G6" s="5">
         <v>2</v>
       </c>
       <c r="H6" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" s="5">
         <v>0</v>
       </c>
       <c r="J6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" s="5">
         <v>0</v>
       </c>
       <c r="L6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>2</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.3448487732639478</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.3448487732639478</v>
+      </c>
+      <c r="R6" s="5">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4935,14 +8390,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4953,9 +8409,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4989,8 +8451,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -5012,10 +8482,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.3214192584615375</v>
@@ -5053,10 +8541,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.1031209699085593</v>
+      </c>
+      <c r="O3" s="5">
+        <v>16</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2936256787383172</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2583497991431614</v>
+      </c>
+      <c r="R3" s="5">
+        <v>16</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.3577737783110934</v>
@@ -5094,91 +8600,141 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.3454670033453213</v>
+      </c>
+      <c r="O4" s="5">
+        <v>18</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1005214106402289</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.09801626186050766</v>
+      </c>
+      <c r="R4" s="5">
+        <v>18</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
+        <v>0.4468680736063106</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.4618270047649276</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.3522054072855099</v>
+      </c>
+      <c r="E5" s="4">
+        <v>79.33673469387755</v>
+      </c>
+      <c r="F5" s="4">
+        <v>81.14093959731544</v>
+      </c>
+      <c r="G5" s="5">
+        <v>2</v>
+      </c>
+      <c r="H5" s="5">
+        <v>1</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>1</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>1</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4468680736063106</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4618270047649276</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="4">
         <v>0.5042061198582815</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C6" s="4">
         <v>0.5042061198582815</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D6" s="4">
         <v>0.4362792361607717</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E6" s="4">
         <v>77.24489795918367</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F6" s="4">
         <v>83.38926174496645</v>
       </c>
-      <c r="G5" s="5">
-        <v>2</v>
-      </c>
-      <c r="H5" s="5">
-        <v>2</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" s="4">
-        <v>0.4468680736063106</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0.4618270047649276</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0.3522054072855099</v>
-      </c>
-      <c r="E6" s="4">
-        <v>79.33673469387755</v>
-      </c>
-      <c r="F6" s="4">
-        <v>81.14093959731544</v>
-      </c>
       <c r="G6" s="5">
         <v>2</v>
       </c>
       <c r="H6" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" s="5">
         <v>0</v>
       </c>
       <c r="J6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" s="5">
         <v>0</v>
       </c>
       <c r="L6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>2</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.5042061198582815</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.5042061198582815</v>
+      </c>
+      <c r="R6" s="5">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -5189,14 +8745,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -5207,9 +8764,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -5243,8 +8806,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -5266,10 +8837,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.228429741106811</v>
@@ -5307,10 +8896,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.07160883458855097</v>
+      </c>
+      <c r="O3" s="5">
+        <v>20</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.228429741106811</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.228429741106811</v>
+      </c>
+      <c r="R3" s="5">
+        <v>20</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.1352088903106051</v>
@@ -5348,67 +8955,101 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.1352088903106051</v>
+      </c>
+      <c r="O4" s="5">
+        <v>20</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.04569748658905155</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.04569748658905155</v>
+      </c>
+      <c r="R4" s="5">
+        <v>20</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
+        <v>0.1347104426859005</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.1347104426859005</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.119809758329211</v>
+      </c>
+      <c r="E5" s="4">
+        <v>85.66326530612245</v>
+      </c>
+      <c r="F5" s="4">
+        <v>91.01230425055927</v>
+      </c>
+      <c r="G5" s="5">
+        <v>2</v>
+      </c>
+      <c r="H5" s="5">
+        <v>2</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1347104426859005</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1347104426859005</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="4">
         <v>0.2166976321568654</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C6" s="4">
         <v>0.2166976321568654</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D6" s="4">
         <v>0.1961032737126516</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E6" s="4">
         <v>85.71428571428571</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F6" s="4">
         <v>89.42393736017897</v>
       </c>
-      <c r="G5" s="5">
-        <v>2</v>
-      </c>
-      <c r="H5" s="5">
-        <v>2</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" s="4">
-        <v>0.1347104426859005</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0.1347104426859005</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0.119809758329211</v>
-      </c>
-      <c r="E6" s="4">
-        <v>85.66326530612245</v>
-      </c>
-      <c r="F6" s="4">
-        <v>91.01230425055927</v>
-      </c>
       <c r="G6" s="5">
         <v>2</v>
       </c>
@@ -5430,9 +9071,25 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>2</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.2166976321568654</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.2166976321568654</v>
+      </c>
+      <c r="R6" s="5">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -5443,514 +9100,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.298669344523239</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.298669344523239</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.288882139021684</v>
-      </c>
-      <c r="E3" s="4">
-        <v>81.48979591836735</v>
-      </c>
-      <c r="F3" s="4">
-        <v>87.42281879194631</v>
-      </c>
-      <c r="G3" s="5">
-        <v>20</v>
-      </c>
-      <c r="H3" s="5">
-        <v>20</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.1555177566159034</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.1558190126294164</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.1584512813345568</v>
-      </c>
-      <c r="E4" s="4">
-        <v>78.85714285714286</v>
-      </c>
-      <c r="F4" s="4">
-        <v>82.53355704697987</v>
-      </c>
-      <c r="G4" s="5">
-        <v>20</v>
-      </c>
-      <c r="H4" s="5">
-        <v>18</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>2</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>2</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.6005282069775575</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.6005282069775575</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.5703303222093155</v>
-      </c>
-      <c r="E5" s="4">
-        <v>81.68367346938776</v>
-      </c>
-      <c r="F5" s="4">
-        <v>86.94630872483222</v>
-      </c>
-      <c r="G5" s="5">
-        <v>2</v>
-      </c>
-      <c r="H5" s="5">
-        <v>2</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" s="4">
-        <v>0.6446740862379556</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0.696229585707357</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0.6042380183290632</v>
-      </c>
-      <c r="E6" s="4">
-        <v>82.34693877551021</v>
-      </c>
-      <c r="F6" s="4">
-        <v>82.56711409395973</v>
-      </c>
-      <c r="G6" s="5">
-        <v>2</v>
-      </c>
-      <c r="H6" s="5">
-        <v>1</v>
-      </c>
-      <c r="I6" s="5">
-        <v>0</v>
-      </c>
-      <c r="J6" s="5">
-        <v>1</v>
-      </c>
-      <c r="K6" s="5">
-        <v>0</v>
-      </c>
-      <c r="L6" s="5">
-        <v>1</v>
-      </c>
-      <c r="M6" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.6863954031010507</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.6904562368411765</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.7830121159626288</v>
-      </c>
-      <c r="E3" s="4">
-        <v>78.01020408163265</v>
-      </c>
-      <c r="F3" s="4">
-        <v>78.36744966442951</v>
-      </c>
-      <c r="G3" s="5">
-        <v>20</v>
-      </c>
-      <c r="H3" s="5">
-        <v>12</v>
-      </c>
-      <c r="I3" s="5">
-        <v>8</v>
-      </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.2760957285187032</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.2051281206493311</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.2052912315564754</v>
-      </c>
-      <c r="E4" s="4">
-        <v>76.70408163265306</v>
-      </c>
-      <c r="F4" s="4">
-        <v>81.89597315436242</v>
-      </c>
-      <c r="G4" s="5">
-        <v>20</v>
-      </c>
-      <c r="H4" s="5">
-        <v>18</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>2</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>2</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.05520396037536557</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.05520396037536557</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.06447702757213847</v>
-      </c>
-      <c r="E5" s="4">
-        <v>79.69387755102041</v>
-      </c>
-      <c r="F5" s="4">
-        <v>84.9496644295302</v>
-      </c>
-      <c r="G5" s="5">
-        <v>2</v>
-      </c>
-      <c r="H5" s="5">
-        <v>2</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" s="4">
-        <v>0.4362269755838497</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0.3532435544475447</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0.3430253383157833</v>
-      </c>
-      <c r="E6" s="4">
-        <v>76.78571428571429</v>
-      </c>
-      <c r="F6" s="4">
-        <v>79.74832214765101</v>
-      </c>
-      <c r="G6" s="5">
-        <v>2</v>
-      </c>
-      <c r="H6" s="5">
-        <v>1</v>
-      </c>
-      <c r="I6" s="5">
-        <v>0</v>
-      </c>
-      <c r="J6" s="5">
-        <v>1</v>
-      </c>
-      <c r="K6" s="5">
-        <v>0</v>
-      </c>
-      <c r="L6" s="5">
-        <v>1</v>
-      </c>
-      <c r="M6" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/downloads/SniderRevealing2018.xlsx
+++ b/public/downloads/SniderRevealing2018.xlsx
@@ -1560,16 +1560,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2191137208338517</v>
+        <v>-0.1972065868655477</v>
       </c>
       <c r="O3" s="5">
         <v>20</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2117906267152352</v>
+        <v>0.2091710453935647</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2117906267152352</v>
+        <v>0.2091710453935647</v>
       </c>
       <c r="R3" s="5">
         <v>20</v>
@@ -1619,7 +1619,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.06219259478024202</v>
+        <v>0.06375479975968545</v>
       </c>
       <c r="O4" s="5">
         <v>18</v>
@@ -1915,7 +1915,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.4711362930647738</v>
+        <v>0.3668912734938203</v>
       </c>
       <c r="O3" s="5">
         <v>12</v>
@@ -1974,16 +1974,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1297706228397146</v>
+        <v>-0.02934120276768226</v>
       </c>
       <c r="O4" s="5">
         <v>18</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2787810792055098</v>
+        <v>0.2706024574428739</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2225308017279733</v>
+        <v>0.2022846197614854</v>
       </c>
       <c r="R4" s="5">
         <v>18</v>
@@ -2270,7 +2270,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.002919056120803276</v>
+        <v>0.02889605140444473</v>
       </c>
       <c r="O3" s="5">
         <v>20</v>
@@ -2329,16 +2329,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.06302054907877533</v>
+        <v>-0.06460903416341246</v>
       </c>
       <c r="O4" s="5">
         <v>20</v>
       </c>
       <c r="P4" s="4">
-        <v>0.05247879080442373</v>
+        <v>0.05240060168560867</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.05247879080442373</v>
+        <v>0.05240060168560867</v>
       </c>
       <c r="R4" s="5">
         <v>20</v>
@@ -2625,13 +2625,13 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1549077861792674</v>
+        <v>0.1642837320177932</v>
       </c>
       <c r="O3" s="5">
         <v>14</v>
       </c>
       <c r="P3" s="4">
-        <v>0.271944070689746</v>
+        <v>0.2728816652735986</v>
       </c>
       <c r="Q3" s="4">
         <v>0.2711607741595279</v>
@@ -2684,7 +2684,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.4112620634437008</v>
+        <v>0.3140584075990773</v>
       </c>
       <c r="O4" s="5">
         <v>16</v>
@@ -2980,16 +2980,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.07299230359785724</v>
+        <v>-0.09056554357448476</v>
       </c>
       <c r="O3" s="5">
         <v>16</v>
       </c>
       <c r="P3" s="4">
-        <v>0.253571407313575</v>
+        <v>0.2511388910650567</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2435734724404028</v>
+        <v>0.2423211157265541</v>
       </c>
       <c r="R3" s="5">
         <v>16</v>
@@ -3039,16 +3039,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1301571344054537</v>
+        <v>-0.125888245911483</v>
       </c>
       <c r="O4" s="5">
         <v>20</v>
       </c>
       <c r="P4" s="4">
-        <v>0.04020372320723253</v>
+        <v>0.03970680116835865</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.04020372320723253</v>
+        <v>0.03970680116835865</v>
       </c>
       <c r="R4" s="5">
         <v>20</v>
@@ -3335,7 +3335,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.08684748467082197</v>
+        <v>0.04750128482555738</v>
       </c>
       <c r="O3" s="5">
         <v>12</v>
@@ -3394,16 +3394,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2736160353059758</v>
+        <v>-0.2579595881725254</v>
       </c>
       <c r="O4" s="5">
         <v>18</v>
       </c>
       <c r="P4" s="4">
-        <v>0.06178631474031136</v>
+        <v>0.06197737461152428</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.04664201973364358</v>
+        <v>0.04511470324238568</v>
       </c>
       <c r="R4" s="5">
         <v>18</v>
@@ -3690,7 +3690,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.07375102428195106</v>
+        <v>-0.07349623548726214</v>
       </c>
       <c r="O3" s="5">
         <v>20</v>
@@ -3749,7 +3749,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1610849288321332</v>
+        <v>-0.1617867106542761</v>
       </c>
       <c r="O4" s="5">
         <v>20</v>
@@ -4045,16 +4045,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3731938422977649</v>
+        <v>-0.4168378186514019</v>
       </c>
       <c r="O3" s="5">
         <v>20</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1840088869428985</v>
+        <v>0.1772408742246611</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1840088869428985</v>
+        <v>0.1772408742246611</v>
       </c>
       <c r="R3" s="5">
         <v>20</v>
@@ -4104,7 +4104,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1960027177847193</v>
+        <v>-0.1377869991229126</v>
       </c>
       <c r="O4" s="5">
         <v>20</v>
@@ -4400,16 +4400,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.0784478544131291</v>
+        <v>-0.07998197416961261</v>
       </c>
       <c r="O3" s="5">
         <v>18</v>
       </c>
       <c r="P3" s="4">
-        <v>0.02834596981558046</v>
+        <v>0.02804822938234395</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.01931494752246291</v>
+        <v>0.01915458256958718</v>
       </c>
       <c r="R3" s="5">
         <v>18</v>
@@ -4459,7 +4459,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1098028098262076</v>
+        <v>-0.1178982338678836</v>
       </c>
       <c r="O4" s="5">
         <v>20</v>
@@ -4755,13 +4755,13 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.902750490601635</v>
+        <v>-0.9106760179056295</v>
       </c>
       <c r="O3" s="5">
         <v>16</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1751227406190072</v>
+        <v>0.1767078460798061</v>
       </c>
       <c r="Q3" s="4">
         <v>0.08244913149974487</v>
@@ -4814,16 +4814,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.5520360668218898</v>
+        <v>-0.5357966856427083</v>
       </c>
       <c r="O4" s="5">
         <v>20</v>
       </c>
       <c r="P4" s="4">
-        <v>0.04490845520238858</v>
+        <v>0.04244015967197345</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.04490845520238858</v>
+        <v>0.04244015967197345</v>
       </c>
       <c r="R4" s="5">
         <v>20</v>
@@ -5074,13 +5074,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <v>0.3599549377728677</v>
+        <v>0.3591715681627234</v>
       </c>
       <c r="I3" s="4">
-        <v>0.3276457334354815</v>
+        <v>0.3267619318240367</v>
       </c>
       <c r="J3" s="4">
-        <v>0.355761315665396</v>
+        <v>0.3576856544180125</v>
       </c>
       <c r="K3" s="4">
         <v>75.19867037724153</v>
@@ -5124,13 +5124,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <v>0.3100930322523948</v>
+        <v>0.3087461237419947</v>
       </c>
       <c r="I4" s="4">
-        <v>0.3090278244371928</v>
+        <v>0.3077977618122532</v>
       </c>
       <c r="J4" s="4">
-        <v>0.3039036996342474</v>
+        <v>0.3039036996342475</v>
       </c>
       <c r="K4" s="4">
         <v>71.66589363017921</v>
@@ -5174,13 +5174,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <v>0.1835500697338747</v>
+        <v>0.1832432934788812</v>
       </c>
       <c r="I5" s="4">
-        <v>0.1799702331737868</v>
+        <v>0.179641009875745</v>
       </c>
       <c r="J5" s="4">
-        <v>0.1835430060814866</v>
+        <v>0.1821252122729427</v>
       </c>
       <c r="K5" s="4">
         <v>76.40769944341376</v>
@@ -5224,13 +5224,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <v>0.2223884130568206</v>
+        <v>0.2217204271123178</v>
       </c>
       <c r="I6" s="4">
-        <v>0.1991386147097624</v>
+        <v>0.1969948815977487</v>
       </c>
       <c r="J6" s="4">
-        <v>0.1960557122530107</v>
+        <v>0.1957563980858223</v>
       </c>
       <c r="K6" s="4">
         <v>77.79993815708099</v>
@@ -5280,7 +5280,7 @@
         <v>0.140576379627336</v>
       </c>
       <c r="J7" s="4">
-        <v>0.1394942020526453</v>
+        <v>0.1391032279656925</v>
       </c>
       <c r="K7" s="4">
         <v>82.23252937538638</v>
@@ -5324,13 +5324,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <v>0.2223260493333208</v>
+        <v>0.2211353305507432</v>
       </c>
       <c r="I8" s="4">
-        <v>0.2166735287538777</v>
+        <v>0.2153956842067214</v>
       </c>
       <c r="J8" s="4">
-        <v>0.2212269067087045</v>
+        <v>0.2184751373284351</v>
       </c>
       <c r="K8" s="4">
         <v>80.34090909090881</v>
@@ -5374,13 +5374,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <v>0.4491117917972257</v>
+        <v>0.445394236450573</v>
       </c>
       <c r="I9" s="4">
-        <v>0.3754736519708372</v>
+        <v>0.3644302799891165</v>
       </c>
       <c r="J9" s="4">
-        <v>0.4233965930943668</v>
+        <v>0.4140097312189358</v>
       </c>
       <c r="K9" s="4">
         <v>77.43738404452662</v>
@@ -5424,10 +5424,10 @@
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <v>0.1235285690285322</v>
+        <v>0.1234930285199799</v>
       </c>
       <c r="I10" s="4">
-        <v>0.1246276275891738</v>
+        <v>0.1245912605571668</v>
       </c>
       <c r="J10" s="4">
         <v>0.1211860805790805</v>
@@ -5474,13 +5474,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <v>0.4311161358422538</v>
+        <v>0.4315423151985504</v>
       </c>
       <c r="I11" s="4">
         <v>0.4446452326965025</v>
       </c>
       <c r="J11" s="4">
-        <v>0.4265318754944207</v>
+        <v>0.4261056961381242</v>
       </c>
       <c r="K11" s="4">
         <v>77.28200371057486</v>
@@ -5524,13 +5524,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <v>0.1440795588968533</v>
+        <v>0.1427479960389477</v>
       </c>
       <c r="I12" s="4">
-        <v>0.1318725568903177</v>
+        <v>0.1311039377057265</v>
       </c>
       <c r="J12" s="4">
-        <v>0.1394077549714315</v>
+        <v>0.1404840785861862</v>
       </c>
       <c r="K12" s="4">
         <v>81.52906617192339</v>
@@ -5574,13 +5574,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <v>0.2716227979333119</v>
+        <v>0.2717096433293177</v>
       </c>
       <c r="I13" s="4">
-        <v>0.2340209545154935</v>
+        <v>0.2331878727929892</v>
       </c>
       <c r="J13" s="4">
-        <v>0.2676605714193533</v>
+        <v>0.2648296353270945</v>
       </c>
       <c r="K13" s="4">
         <v>75.3239022881877</v>
@@ -5630,7 +5630,7 @@
         <v>0.05039543237183994</v>
       </c>
       <c r="J14" s="4">
-        <v>0.04872629048146719</v>
+        <v>0.04871251261135061</v>
       </c>
       <c r="K14" s="4">
         <v>99.4712430426716</v>
@@ -5674,13 +5674,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <v>0.2696137285753604</v>
+        <v>0.2665373591579798</v>
       </c>
       <c r="I15" s="4">
-        <v>0.2696137285753604</v>
+        <v>0.2665373591579798</v>
       </c>
       <c r="J15" s="4">
-        <v>0.2838242703926354</v>
+        <v>0.2802678791836494</v>
       </c>
       <c r="K15" s="4">
         <v>77.66388373531221</v>
@@ -5724,13 +5724,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <v>0.04706269744301661</v>
+        <v>0.04692736088245457</v>
       </c>
       <c r="I16" s="4">
-        <v>0.04408353206155843</v>
+        <v>0.04401480422461169</v>
       </c>
       <c r="J16" s="4">
-        <v>0.04434951652023793</v>
+        <v>0.04453104647158859</v>
       </c>
       <c r="K16" s="4">
         <v>97.93367346938749</v>
@@ -5774,13 +5774,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <v>0.1170295775677025</v>
+        <v>0.1166281275360588</v>
       </c>
       <c r="I17" s="4">
-        <v>0.07415081761486715</v>
+        <v>0.07291666984965958</v>
       </c>
       <c r="J17" s="4">
-        <v>0.1481312150508861</v>
+        <v>0.1487034711287636</v>
       </c>
       <c r="K17" s="4">
         <v>76.43475572046967</v>
@@ -7477,7 +7477,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2467236429411059</v>
+        <v>-0.2099709607682598</v>
       </c>
       <c r="O3" s="5">
         <v>16</v>
@@ -7536,16 +7536,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.03865451561578084</v>
+        <v>-0.05661097285337746</v>
       </c>
       <c r="O4" s="5">
         <v>20</v>
       </c>
       <c r="P4" s="4">
-        <v>0.08034995829279068</v>
+        <v>0.07862654515047325</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.08034995829279068</v>
+        <v>0.07862654515047325</v>
       </c>
       <c r="R4" s="5">
         <v>20</v>
@@ -7832,16 +7832,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.04198092905280646</v>
+        <v>-0.01336589340280625</v>
       </c>
       <c r="O3" s="5">
         <v>20</v>
       </c>
       <c r="P3" s="4">
-        <v>0.4038421182862657</v>
+        <v>0.401563657605584</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.4038421182862657</v>
+        <v>0.401563657605584</v>
       </c>
       <c r="R3" s="5">
         <v>20</v>
@@ -7891,16 +7891,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.122591031448893</v>
+        <v>-0.1263917035539635</v>
       </c>
       <c r="O4" s="5">
         <v>18</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1843790385044283</v>
+        <v>0.1836943004622299</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1679253320747384</v>
+        <v>0.1675868089284146</v>
       </c>
       <c r="R4" s="5">
         <v>18</v>
@@ -8187,7 +8187,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.07045535815187678</v>
+        <v>-0.04872651765981573</v>
       </c>
       <c r="O3" s="5">
         <v>18</v>
@@ -8246,16 +8246,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.3574975137627917</v>
+        <v>-0.3834261985466583</v>
       </c>
       <c r="O4" s="5">
         <v>20</v>
       </c>
       <c r="P4" s="4">
-        <v>0.09366816858062521</v>
+        <v>0.09299326081963954</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.09366816858062521</v>
+        <v>0.09299326081963954</v>
       </c>
       <c r="R4" s="5">
         <v>20</v>
@@ -8542,16 +8542,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1031209699085593</v>
+        <v>-0.07332835468332632</v>
       </c>
       <c r="O3" s="5">
         <v>16</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2936256787383172</v>
+        <v>0.29748501668073</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2583497991431614</v>
+        <v>0.2557258177648691</v>
       </c>
       <c r="R3" s="5">
         <v>16</v>
@@ -8601,16 +8601,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.3454670033453213</v>
+        <v>-0.3800888620025944</v>
       </c>
       <c r="O4" s="5">
         <v>18</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1005214106402289</v>
+        <v>0.09519250361990998</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.09801626186050766</v>
+        <v>0.09594212724429478</v>
       </c>
       <c r="R4" s="5">
         <v>18</v>
@@ -8897,7 +8897,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.07160883458855097</v>
+        <v>0.1052266773185693</v>
       </c>
       <c r="O3" s="5">
         <v>20</v>
@@ -8956,7 +8956,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1352088903106051</v>
+        <v>-0.133058532832365</v>
       </c>
       <c r="O4" s="5">
         <v>20</v>
